--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0024.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0024.xlsx
@@ -1484,7 +1484,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Khu vực này trên bản đồ đã chuyển sang màu đỏ, {PlayerName}. Số lượng báo cáo từ các tín使 cũng tăng lên.</t>
+          <t>Khu vực này trên bản đồ đã chuyển sang màu đỏ, {PlayerName}. Số lượng báo cáo từ các tín sứ cũng tăng lên.</t>
         </is>
       </c>
     </row>
@@ -4604,7 +4604,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>Gì cơ? V... Rover...</t>
+          <t>Gì cơ? V... Vận Mệnh Giả...</t>
         </is>
       </c>
     </row>
@@ -5124,7 +5124,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>Rover vừa đến nơi. {Male=Anh ấy;Female=Cô ấy} chính là người chúng ta đã mời trước đó—Cộng Hưởng Giả bí ẩn xuất hiện ở Jinzhou.</t>
+          <t>Vận Mệnh Giả vừa đến nơi. {Male=He;Female=She} chính là người chúng ta đã mời trước đó—Resonator bí ẩn xuất hiện ở Jinzhou.</t>
         </is>
       </c>
     </row>
@@ -5189,7 +5189,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>Vậy là cậu chính là Cộng Hưởng Giả đã đối đầu với Threnodian à? Thật lòng mà nói, ta không ngờ sẽ được gặp cậu trực tiếp đấy!</t>
+          <t>Vậy là cậu chính là Resonator đã đối đầu với Threnodian à? Thật lòng mà nói, ta không ngờ sẽ được gặp cậu trực tiếp đấy!</t>
         </is>
       </c>
     </row>
@@ -7074,7 +7074,7 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>Aalto à? Ta đã bảo ngươi rồi, khi nói đến mấy trò cổ điển trên TR-1200, ngươi chẳng có cửa đâu! Một chút cơ hội cũng không có!</t>
+          <t>Aalto à? Tao đã bảo mày rồi, khi nói đến mấy trò cổ điển trên TR-1200, mày chẳng có cửa đâu! Một chút cơ hội cũng không có!</t>
         </is>
       </c>
     </row>
@@ -7204,7 +7204,7 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>Này, khoan đã! Đừng có gọi ta thế! Mọi động thái của ta đều là để gom chip cho Black Shores đấy!</t>
+          <t>Này, khoan đã! Đừng có gọi tao thế! Mọi động thái của tao đều là để gom chip cho Black Shores đấy!</t>
         </is>
       </c>
     </row>
@@ -7334,7 +7334,7 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>Kiểm soát trọng lực á? Nghe viển vông quá. Ta thà tin có kẻ đúc tiền Shell Credits còn hơn.</t>
+          <t>Kiểm soát trọng lực á? Nghe viển vông quá. Tao thà tin có kẻ đúc tiền Shell Credits còn hơn.</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>Chắc chắn rồi! Tiền Shell Credits chúng kiếm được, chia 30-70 nhé. Tôi lấy 70, cậu lấy 30. Thế là xong giao kèo!</t>
+          <t>Chắc chắn rồi! Shell Credit Shell Credits chúng kiếm được, chia 30-70 nhé. Tôi lấy 70, cậu lấy 30. Thế là xong giao kèo!</t>
         </is>
       </c>
     </row>
@@ -7724,7 +7724,7 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>Còn Hoda... Nếu cô ấy là một Bloom Bearer, hệ thống chắc chắn phải có hồ sơ về cô ấy. Và nếu một Cộng Hưởng Giả như vậy tồn tại, Black Shores ắt hẳn đã biết rồi.</t>
+          <t>Còn Hoda... Nếu cô ấy là một Bloom Bearer, hệ thống chắc chắn phải có hồ sơ về cô ấy. Và nếu một Resonator như vậy tồn tại, Black Shores ắt hẳn đã biết rồi.</t>
         </is>
       </c>
     </row>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>Có chuyện gì thế, Aalto? Ta chưa bao giờ thấy ngươi nghiêm túc như vậy.</t>
+          <t>Có chuyện gì thế, Aalto? Tao chưa bao giờ thấy mày nghiêm túc như vậy.</t>
         </is>
       </c>
     </row>
@@ -10909,7 +10909,7 @@
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>À! Rover, cuối cùng cậu cũng đến...</t>
+          <t>À! Vận Mệnh Giả, cuối cùng cậu cũng đến...</t>
         </is>
       </c>
     </row>
@@ -10974,7 +10974,7 @@
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>Vậy là cậu chính là Rover à? Rất vui được gặp cậu.</t>
+          <t>Vậy là cậu chính là Vận Mệnh Giả à? Rất vui được gặp cậu.</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>Ừ, ta nhớ cậu từng nói muốn tìm hiểu thêm về quá khứ liên quan đến Bờ Biển Đen.</t>
+          <t>Ừ, tao nhớ cậu từng nói muốn tìm hiểu thêm về quá khứ liên quan đến Bờ Biển Đen.</t>
         </is>
       </c>
     </row>
@@ -12469,7 +12469,7 @@
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t>Thư giãn đi, ta chỉ đùa thôi. Này {PlayerName}, ngươi cũng đang truy tìm Bãi Đen à?</t>
+          <t>Thư giãn đi, tao chỉ đùa thôi. Này {PlayerName}, mày cũng đang truy tìm Bãi Đen à?</t>
         </is>
       </c>
     </row>
@@ -12534,7 +12534,7 @@
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>Ta tưởng một tay môi giới thông tin như ngươi lúc nào cũng tỉnh táo lạnh lùng cơ chứ.</t>
+          <t>Tao tưởng một tay môi giới thông tin như mày lúc nào cũng tỉnh táo lạnh lùng cơ chứ.</t>
         </is>
       </c>
     </row>
@@ -13119,7 +13119,7 @@
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>Thật sao?</t>
+          <t>Thật chứ?</t>
         </is>
       </c>
     </row>
@@ -14809,7 +14809,7 @@
       </c>
       <c r="M221" t="inlineStr">
         <is>
-          <t>Đợi đã! KU-Nước, cậu có cảm giác đó không? Cậu... cậu cũng thấy giống ta đúng không?</t>
+          <t>Đợi đã! KU-Nước, cậu có cảm giác đó không? Cậu... cậu cũng thấy giống tao đúng không?</t>
         </is>
       </c>
     </row>
@@ -18644,7 +18644,7 @@
       </c>
       <c r="M280" t="inlineStr">
         <is>
-          <t>Ta nghe thấy tiếng vọng của những Cộng Hưởng Giả mà ta từng thu thập trong mớ tần số rải rác này.</t>
+          <t>Tao nghe thấy tiếng vọng của những Cộng Hưởng Giả mà tao từng thu thập trong mớ tần số rải rác này.</t>
         </is>
       </c>
     </row>
@@ -19034,7 +19034,7 @@
       </c>
       <c r="M286" t="inlineStr">
         <is>
-          <t>Ngươi có giấy phép gì không? Ta biết là không rồi.</t>
+          <t>Mày có giấy phép gì không? Tao biết là không rồi.</t>
         </is>
       </c>
     </row>
@@ -19099,7 +19099,7 @@
       </c>
       <c r="M287" t="inlineStr">
         <is>
-          <t>Đừng lại gần quá, không là nó làm cậu toi đấy.</t>
+          <t>Đừng lại gần quá, không là nó làm mày toi đấy.</t>
         </is>
       </c>
     </row>
@@ -19684,7 +19684,7 @@
       </c>
       <c r="M296" t="inlineStr">
         <is>
-          <t>Ta đã thấy Mưa Retroact ở Jinzhou rồi.</t>
+          <t>Tao đã thấy Mưa Retroact ở Jinzhou rồi.</t>
         </is>
       </c>
     </row>
@@ -26704,7 +26704,7 @@
       </c>
       <c r="M404" t="inlineStr">
         <is>
-          <t>Có thể là Tiếng Vang từ các Quả Cầu Sonoro.</t>
+          <t>Có thể là Tiếng Vang từ các Sonoro Sphere.</t>
         </is>
       </c>
     </row>
@@ -27744,7 +27744,7 @@
       </c>
       <c r="M420" t="inlineStr">
         <is>
-          <t>Cảm ơn cậu! Có một Rover thuộc Midnight Ranger ở đây thật yên tâm. Tớ sẽ gửi tọa độ của tần số bất thường cho cậu ngay.</t>
+          <t>Cảm ơn cậu! Có một Vận Mệnh Giả thuộc Midnight Ranger ở đây thật yên tâm. Tớ sẽ gửi tọa độ của tần số bất thường cho cậu ngay.</t>
         </is>
       </c>
     </row>
@@ -30214,7 +30214,7 @@
       </c>
       <c r="M458" t="inlineStr">
         <is>
-          <t>Ta sẽ đưa nó cho Người Gác Bờ.</t>
+          <t>Tao sẽ đưa nó cho Người Gác Bờ.</t>
         </is>
       </c>
     </row>
@@ -32814,7 +32814,7 @@
       </c>
       <c r="M498" t="inlineStr">
         <is>
-          <t>Ngươi vừa gọi ta là gì?</t>
+          <t>Mày vừa gọi tao là gì?</t>
         </is>
       </c>
     </row>
